--- a/data/proteomics/volume_size_across_compartment_jianye_C_limitation.xlsx
+++ b/data/proteomics/volume_size_across_compartment_jianye_C_limitation.xlsx
@@ -493,13 +493,13 @@
         <v>1.435060245377138</v>
       </c>
       <c r="D2" t="n">
-        <v>1.482494429737002</v>
+        <v>1.482494429737001</v>
       </c>
       <c r="E2" t="n">
-        <v>1.525391204846452</v>
+        <v>1.525391204846453</v>
       </c>
       <c r="F2" t="n">
-        <v>1.60968740935172</v>
+        <v>1.609687409351717</v>
       </c>
       <c r="G2" t="n">
         <v>1.147433317235545</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.002767469536885725</v>
+        <v>0.002767469536885726</v>
       </c>
       <c r="D3" t="n">
         <v>0.002799267427805039</v>
@@ -536,7 +536,7 @@
         <v>0.003046404086363977</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003332187725180592</v>
+        <v>0.003332187725180593</v>
       </c>
       <c r="G3" t="n">
         <v>0.002391106777092708</v>
@@ -573,10 +573,10 @@
         <v>0.003725699867309978</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003845668605429031</v>
+        <v>0.00384566860542903</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003172467717915093</v>
+        <v>0.003172467717915094</v>
       </c>
       <c r="H4" t="n">
         <v>0.003452656612891943</v>
@@ -638,31 +638,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8146077370416355</v>
+        <v>0.8146077370416362</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8024095002558804</v>
+        <v>0.8024095002558786</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7778556305414942</v>
+        <v>0.7778556305414948</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7921225404128416</v>
+        <v>0.7921225404128402</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5440598804781426</v>
+        <v>0.5440598804781421</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5900364049992808</v>
+        <v>0.5900364049992805</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6028068738115888</v>
+        <v>0.6028068738115898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6181845004615639</v>
+        <v>0.6181845004615636</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5644020069975343</v>
+        <v>0.5644020069975346</v>
       </c>
     </row>
     <row r="7">
@@ -678,28 +678,28 @@
         <v>1.754824598079164</v>
       </c>
       <c r="D7" t="n">
-        <v>1.775057914759795</v>
+        <v>1.775057914759797</v>
       </c>
       <c r="E7" t="n">
-        <v>1.862761828771688</v>
+        <v>1.86276182877169</v>
       </c>
       <c r="F7" t="n">
-        <v>2.002849848230755</v>
+        <v>2.002849848230758</v>
       </c>
       <c r="G7" t="n">
-        <v>1.447956491732565</v>
+        <v>1.447956491732567</v>
       </c>
       <c r="H7" t="n">
-        <v>1.656399060767537</v>
+        <v>1.656399060767539</v>
       </c>
       <c r="I7" t="n">
         <v>1.713838046107555</v>
       </c>
       <c r="J7" t="n">
-        <v>1.781725442703078</v>
+        <v>1.781725442703075</v>
       </c>
       <c r="K7" t="n">
-        <v>1.635135843288922</v>
+        <v>1.635135843288921</v>
       </c>
     </row>
     <row r="8">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8802512439551776</v>
+        <v>0.8802512439551787</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9134263496231648</v>
+        <v>0.9134263496231646</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8999355368943829</v>
+        <v>0.8999355368943832</v>
       </c>
       <c r="F8" t="n">
         <v>0.9261767671020885</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6293086811561069</v>
+        <v>0.6293086811561066</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6831597238167803</v>
+        <v>0.6831597238167804</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7197487212354396</v>
+        <v>0.7197487212354392</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7155231377424059</v>
+        <v>0.7155231377424062</v>
       </c>
       <c r="K8" t="n">
         <v>0.6384210132725686</v>
@@ -838,7 +838,7 @@
         <v>0.09745411029723122</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09721187146040261</v>
+        <v>0.0972118714604026</v>
       </c>
       <c r="I11" t="n">
         <v>0.09787642275670719</v>
@@ -847,7 +847,7 @@
         <v>0.09981932227404364</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08511021916488389</v>
+        <v>0.0851102191648839</v>
       </c>
     </row>
     <row r="12">
@@ -860,31 +860,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.08203051869934909</v>
+        <v>0.0820305186993491</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08881116557510986</v>
+        <v>0.08881116557510975</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1082190938985385</v>
+        <v>0.1082190938985384</v>
       </c>
       <c r="F12" t="n">
         <v>0.1135865093766597</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07598625334387854</v>
+        <v>0.07598625334387851</v>
       </c>
       <c r="H12" t="n">
-        <v>0.07619711563857608</v>
+        <v>0.07619711563857604</v>
       </c>
       <c r="I12" t="n">
         <v>0.07099489997708741</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06863361666785121</v>
+        <v>0.0686336166678512</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06150386873764219</v>
+        <v>0.0615038687376422</v>
       </c>
     </row>
     <row r="13">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002556644404575217</v>
+        <v>0.002556644404575218</v>
       </c>
       <c r="D13" t="n">
         <v>0.003086014269566292</v>
@@ -912,7 +912,7 @@
         <v>0.003936047578148125</v>
       </c>
       <c r="H13" t="n">
-        <v>0.004561148094540205</v>
+        <v>0.004561148094540206</v>
       </c>
       <c r="I13" t="n">
         <v>0.004179354516756487</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.07553315834110265</v>
+        <v>0.07553315834110262</v>
       </c>
       <c r="D14" t="n">
         <v>0.07941922207771414</v>
@@ -943,7 +943,7 @@
         <v>0.08638397842067326</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08847998295152978</v>
+        <v>0.0884799829515298</v>
       </c>
       <c r="G14" t="n">
         <v>0.06127434373871082</v>
@@ -952,13 +952,13 @@
         <v>0.06350359348021091</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05858793381411142</v>
+        <v>0.05858793381411141</v>
       </c>
       <c r="J14" t="n">
-        <v>0.05370892524651696</v>
+        <v>0.05370892524651697</v>
       </c>
       <c r="K14" t="n">
-        <v>0.04416308873836201</v>
+        <v>0.04416308873836202</v>
       </c>
     </row>
     <row r="15">
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03503422212668562</v>
+        <v>0.03503422212668561</v>
       </c>
       <c r="D15" t="n">
         <v>0.03517075139682888</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03432229436328274</v>
+        <v>0.03432229436328273</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03531563064346967</v>
+        <v>0.03531563064346966</v>
       </c>
       <c r="G15" t="n">
         <v>0.02520430180591554</v>
@@ -995,7 +995,7 @@
         <v>0.0262320106781413</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01956197166654732</v>
+        <v>0.01956197166654731</v>
       </c>
     </row>
     <row r="16">
@@ -1023,7 +1023,7 @@
         <v>0.01336197159672077</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01377591400920731</v>
+        <v>0.0137759140092073</v>
       </c>
       <c r="I16" t="n">
         <v>0.01516959215334689</v>
@@ -1051,7 +1051,7 @@
         <v>0.0118472033311431</v>
       </c>
       <c r="E17" t="n">
-        <v>0.009654223687214093</v>
+        <v>0.009654223687214095</v>
       </c>
       <c r="F17" t="n">
         <v>0.008629175235787115</v>
@@ -1063,13 +1063,13 @@
         <v>0.004737802022695277</v>
       </c>
       <c r="I17" t="n">
-        <v>0.004966702777830951</v>
+        <v>0.00496670277783095</v>
       </c>
       <c r="J17" t="n">
-        <v>0.004541737114710873</v>
+        <v>0.004541737114710874</v>
       </c>
       <c r="K17" t="n">
-        <v>0.004121841220470233</v>
+        <v>0.004121841220470234</v>
       </c>
     </row>
     <row r="18">
@@ -1091,7 +1091,7 @@
         <v>0.0196578286642348</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02099573238624741</v>
+        <v>0.02099573238624739</v>
       </c>
       <c r="G18" t="n">
         <v>0.01552884225188183</v>
@@ -1106,7 +1106,7 @@
         <v>0.01687106735276621</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01485235918724213</v>
+        <v>0.01485235918724214</v>
       </c>
     </row>
     <row r="19">
@@ -1125,10 +1125,10 @@
         <v>0.0186258081195577</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02252402217271974</v>
+        <v>0.02252402217271976</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02421336097997628</v>
+        <v>0.02421336097997627</v>
       </c>
       <c r="G19" t="n">
         <v>0.01835291018531332</v>
@@ -1174,10 +1174,10 @@
         <v>0.04402105774092042</v>
       </c>
       <c r="I20" t="n">
-        <v>0.04531006713334266</v>
+        <v>0.04531006713334264</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04813019741316196</v>
+        <v>0.04813019741316197</v>
       </c>
       <c r="K20" t="n">
         <v>0.04481291874512529</v>
@@ -1233,7 +1233,7 @@
         <v>0.005572705547566835</v>
       </c>
       <c r="D22" t="n">
-        <v>0.005365054909434989</v>
+        <v>0.00536505490943499</v>
       </c>
       <c r="E22" t="n">
         <v>0.006534572524364618</v>
@@ -1251,7 +1251,7 @@
         <v>0.005580998379956855</v>
       </c>
       <c r="J22" t="n">
-        <v>0.005177288505981692</v>
+        <v>0.005177288505981691</v>
       </c>
       <c r="K22" t="n">
         <v>0.004407696694260482</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1259739543130061</v>
+        <v>0.125973954313006</v>
       </c>
       <c r="D23" t="n">
         <v>0.1362422377194774</v>
@@ -1282,13 +1282,13 @@
         <v>0.07433286836337193</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07240123043904427</v>
+        <v>0.07240123043904428</v>
       </c>
       <c r="I23" t="n">
-        <v>0.07290078795391179</v>
+        <v>0.07290078795391178</v>
       </c>
       <c r="J23" t="n">
-        <v>0.07314736613607255</v>
+        <v>0.07314736613607252</v>
       </c>
       <c r="K23" t="n">
         <v>0.06565916226043854</v>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0001868169565236403</v>
+        <v>0.0001868169565236402</v>
       </c>
       <c r="D24" t="n">
         <v>0.0002108676737348463</v>
@@ -1319,10 +1319,10 @@
         <v>0.0001831933304584078</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0003330368055156048</v>
+        <v>0.0003330368055156047</v>
       </c>
       <c r="I24" t="n">
-        <v>0.000199286272286162</v>
+        <v>0.0001992862722861619</v>
       </c>
       <c r="J24" t="n">
         <v>0.0002162313317726146</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01523252583807808</v>
+        <v>0.01523252583807809</v>
       </c>
       <c r="D25" t="n">
         <v>0.01520682469293872</v>
@@ -1359,7 +1359,7 @@
         <v>0.01445190766143894</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01505844133709346</v>
+        <v>0.01505844133709345</v>
       </c>
       <c r="J25" t="n">
         <v>0.01574479402961243</v>
@@ -1378,28 +1378,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.005151875351959306</v>
+        <v>0.005151875351959305</v>
       </c>
       <c r="D26" t="n">
         <v>0.00546785418116904</v>
       </c>
       <c r="E26" t="n">
-        <v>0.007007932500540288</v>
+        <v>0.007007932500540289</v>
       </c>
       <c r="F26" t="n">
-        <v>0.007548073285424831</v>
+        <v>0.007548073285424832</v>
       </c>
       <c r="G26" t="n">
-        <v>0.005409150536508751</v>
+        <v>0.00540915053650875</v>
       </c>
       <c r="H26" t="n">
-        <v>0.005867950547297339</v>
+        <v>0.005867950547297338</v>
       </c>
       <c r="I26" t="n">
         <v>0.006041801220696767</v>
       </c>
       <c r="J26" t="n">
-        <v>0.005917048548044243</v>
+        <v>0.005917048548044242</v>
       </c>
       <c r="K26" t="n">
         <v>0.00535935269033228</v>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0569265889022816</v>
+        <v>0.05692658890228158</v>
       </c>
       <c r="D27" t="n">
         <v>0.06081601975375289</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07963873889563415</v>
+        <v>0.07963873889563408</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09388371948560718</v>
+        <v>0.09388371948560716</v>
       </c>
       <c r="G27" t="n">
-        <v>0.07617589987628559</v>
+        <v>0.07617589987628558</v>
       </c>
       <c r="H27" t="n">
-        <v>0.09130177843011671</v>
+        <v>0.09130177843011678</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0970315102287654</v>
+        <v>0.09703151022876537</v>
       </c>
       <c r="J27" t="n">
         <v>0.1038408211603582</v>
       </c>
       <c r="K27" t="n">
-        <v>0.09793945550003727</v>
+        <v>0.09793945550003719</v>
       </c>
     </row>
     <row r="28">
@@ -1461,16 +1461,16 @@
         <v>0.002103198097275929</v>
       </c>
       <c r="F28" t="n">
-        <v>0.002260031493559992</v>
+        <v>0.002260031493559993</v>
       </c>
       <c r="G28" t="n">
         <v>0.001710944706825921</v>
       </c>
       <c r="H28" t="n">
-        <v>0.001953008099310151</v>
+        <v>0.00195300809931015</v>
       </c>
       <c r="I28" t="n">
-        <v>0.001943860499575649</v>
+        <v>0.001943860499575648</v>
       </c>
       <c r="J28" t="n">
         <v>0.001929980310590127</v>
@@ -1489,28 +1489,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.05916594709621302</v>
+        <v>0.05916594709621301</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05943009300267997</v>
+        <v>0.05943009300268</v>
       </c>
       <c r="E29" t="n">
         <v>0.06177493030246273</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06369324727882743</v>
+        <v>0.06369324727882744</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04419890145168229</v>
+        <v>0.04419890145168227</v>
       </c>
       <c r="H29" t="n">
-        <v>0.04807128353562839</v>
+        <v>0.04807128353562836</v>
       </c>
       <c r="I29" t="n">
         <v>0.04518136812256949</v>
       </c>
       <c r="J29" t="n">
-        <v>0.04425943873518566</v>
+        <v>0.04425943873518565</v>
       </c>
       <c r="K29" t="n">
         <v>0.03929858702656722</v>
@@ -1588,7 +1588,7 @@
         <v>0.21135452050791</v>
       </c>
       <c r="E32" t="n">
-        <v>0.218152941608791</v>
+        <v>0.2181529416087911</v>
       </c>
       <c r="F32" t="n">
         <v>0.2337973704252884</v>
@@ -1597,13 +1597,13 @@
         <v>0.1721404758743971</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2026779541591946</v>
+        <v>0.2026779541591945</v>
       </c>
       <c r="I32" t="n">
         <v>0.2210124391955053</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2376460394766454</v>
+        <v>0.2376460394766453</v>
       </c>
       <c r="K32" t="n">
         <v>0.2197453493111749</v>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.07797128145618416</v>
+        <v>0.07797128145618419</v>
       </c>
       <c r="D33" t="n">
         <v>0.08138154673306867</v>
       </c>
       <c r="E33" t="n">
-        <v>0.07385681687734519</v>
+        <v>0.07385681687734516</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07335165341649152</v>
+        <v>0.07335165341649151</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0481276460648684</v>
+        <v>0.04812764606486839</v>
       </c>
       <c r="H33" t="n">
-        <v>0.05258628961397654</v>
+        <v>0.05258628961397653</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0568201211076212</v>
+        <v>0.05682012110762122</v>
       </c>
       <c r="J33" t="n">
         <v>0.05552281879283819</v>
       </c>
       <c r="K33" t="n">
-        <v>0.04742754624029611</v>
+        <v>0.0474275462402961</v>
       </c>
     </row>
     <row r="34">
@@ -1662,13 +1662,13 @@
         <v>0.007958638282211886</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01003462336811607</v>
+        <v>0.01003462336811608</v>
       </c>
       <c r="F34" t="n">
         <v>0.01130513398410671</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00870457281494655</v>
+        <v>0.008704572814946548</v>
       </c>
       <c r="H34" t="n">
         <v>0.009892200895410723</v>
@@ -1699,19 +1699,19 @@
         <v>0.003048368286967352</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003238167481007986</v>
+        <v>0.003238167481007985</v>
       </c>
       <c r="F35" t="n">
-        <v>0.003538599872370982</v>
+        <v>0.003538599872370981</v>
       </c>
       <c r="G35" t="n">
         <v>0.002546007232306169</v>
       </c>
       <c r="H35" t="n">
-        <v>0.002742528066830959</v>
+        <v>0.002742528066830958</v>
       </c>
       <c r="I35" t="n">
-        <v>0.002747680176997362</v>
+        <v>0.002747680176997363</v>
       </c>
       <c r="J35" t="n">
         <v>0.002543149052290604</v>
@@ -1733,22 +1733,22 @@
         <v>0.004604411173846058</v>
       </c>
       <c r="D36" t="n">
-        <v>0.004842985451563332</v>
+        <v>0.00484298545156333</v>
       </c>
       <c r="E36" t="n">
-        <v>0.005730446574542696</v>
+        <v>0.005730446574542697</v>
       </c>
       <c r="F36" t="n">
-        <v>0.006055759916639092</v>
+        <v>0.006055759916639093</v>
       </c>
       <c r="G36" t="n">
-        <v>0.004242683035536615</v>
+        <v>0.004242683035536614</v>
       </c>
       <c r="H36" t="n">
-        <v>0.004610683290965204</v>
+        <v>0.004610683290965203</v>
       </c>
       <c r="I36" t="n">
-        <v>0.004766503790292114</v>
+        <v>0.004766503790292115</v>
       </c>
       <c r="J36" t="n">
         <v>0.00442134127199662</v>
@@ -1779,10 +1779,10 @@
         <v>0.09757920943897924</v>
       </c>
       <c r="G37" t="n">
-        <v>0.07970909197185466</v>
+        <v>0.07970909197185468</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09718576372850016</v>
+        <v>0.09718576372850013</v>
       </c>
       <c r="I37" t="n">
         <v>0.1109405316360906</v>
@@ -1791,7 +1791,7 @@
         <v>0.108770888804825</v>
       </c>
       <c r="K37" t="n">
-        <v>0.08539702707051669</v>
+        <v>0.08539702707051668</v>
       </c>
     </row>
     <row r="38">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.003509663581152034</v>
+        <v>0.003509663581152033</v>
       </c>
       <c r="D38" t="n">
-        <v>0.003464190343898235</v>
+        <v>0.003464190343898234</v>
       </c>
       <c r="E38" t="n">
         <v>0.003581327678003272</v>
@@ -1828,7 +1828,7 @@
         <v>0.003130344163761061</v>
       </c>
       <c r="K38" t="n">
-        <v>0.002869676478201169</v>
+        <v>0.00286967647820117</v>
       </c>
     </row>
     <row r="39">
@@ -1844,7 +1844,7 @@
         <v>0.00155713504318259</v>
       </c>
       <c r="D39" t="n">
-        <v>0.001613095851809941</v>
+        <v>0.001613095851809942</v>
       </c>
       <c r="E39" t="n">
         <v>0.001848226181953896</v>
@@ -1865,7 +1865,7 @@
         <v>0.001426925570090913</v>
       </c>
       <c r="K39" t="n">
-        <v>0.001384941101016626</v>
+        <v>0.001384941101016627</v>
       </c>
     </row>
     <row r="40">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.004362475747569568</v>
+        <v>0.004362475747569569</v>
       </c>
       <c r="D41" t="n">
         <v>0.004483869799620867</v>
       </c>
       <c r="E41" t="n">
-        <v>0.005332372799122903</v>
+        <v>0.005332372799122902</v>
       </c>
       <c r="F41" t="n">
         <v>0.005940157432158645</v>
@@ -1939,7 +1939,7 @@
         <v>0.005062332429926215</v>
       </c>
       <c r="K41" t="n">
-        <v>0.004734118534611894</v>
+        <v>0.004734118534611895</v>
       </c>
     </row>
     <row r="42">
@@ -1964,7 +1964,7 @@
         <v>0.002130277827296005</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001576792900834721</v>
+        <v>0.001576792900834722</v>
       </c>
       <c r="H42" t="n">
         <v>0.001707639722737832</v>
@@ -1989,31 +1989,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.008874664699043416</v>
+        <v>0.008874664699043414</v>
       </c>
       <c r="D43" t="n">
         <v>0.009437668933555734</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01097645526470636</v>
+        <v>0.01097645526470637</v>
       </c>
       <c r="F43" t="n">
         <v>0.01242582982052917</v>
       </c>
       <c r="G43" t="n">
-        <v>0.008477799459114716</v>
+        <v>0.008477799459114718</v>
       </c>
       <c r="H43" t="n">
-        <v>0.009909872730324749</v>
+        <v>0.009909872730324747</v>
       </c>
       <c r="I43" t="n">
-        <v>0.009926811550286763</v>
+        <v>0.009926811550286765</v>
       </c>
       <c r="J43" t="n">
-        <v>0.009283473314980136</v>
+        <v>0.00928347331498014</v>
       </c>
       <c r="K43" t="n">
-        <v>0.008549532540595872</v>
+        <v>0.00854953254059587</v>
       </c>
     </row>
     <row r="44">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.009319912227449233</v>
+        <v>0.009319912227449234</v>
       </c>
       <c r="D44" t="n">
-        <v>0.009638036549904392</v>
+        <v>0.009638036549904394</v>
       </c>
       <c r="E44" t="n">
         <v>0.01135903347753384</v>
@@ -2038,13 +2038,13 @@
         <v>0.01203481999539026</v>
       </c>
       <c r="G44" t="n">
-        <v>0.008826490964873302</v>
+        <v>0.0088264909648733</v>
       </c>
       <c r="H44" t="n">
         <v>0.009526315046264671</v>
       </c>
       <c r="I44" t="n">
-        <v>0.009696445877840899</v>
+        <v>0.009696445877840897</v>
       </c>
       <c r="J44" t="n">
         <v>0.009431602010572601</v>
@@ -2124,7 +2124,7 @@
         <v>0.0005166242351429818</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0004200786650724763</v>
+        <v>0.0004200786650724764</v>
       </c>
     </row>
     <row r="47">
@@ -2189,13 +2189,13 @@
         <v>0.004886640940905592</v>
       </c>
       <c r="H48" t="n">
-        <v>0.004433353384649724</v>
+        <v>0.004433353384649725</v>
       </c>
       <c r="I48" t="n">
         <v>0.003856787212931821</v>
       </c>
       <c r="J48" t="n">
-        <v>0.004109579562588815</v>
+        <v>0.004109579562588816</v>
       </c>
       <c r="K48" t="n">
         <v>0.003672205442329327</v>
@@ -2260,16 +2260,16 @@
         <v>0.005500576689622678</v>
       </c>
       <c r="G50" t="n">
-        <v>0.004089163228555179</v>
+        <v>0.004089163228555178</v>
       </c>
       <c r="H50" t="n">
         <v>0.004873714106569839</v>
       </c>
       <c r="I50" t="n">
-        <v>0.004782727634866158</v>
+        <v>0.004782727634866157</v>
       </c>
       <c r="J50" t="n">
-        <v>0.004914741954493894</v>
+        <v>0.004914741954493893</v>
       </c>
       <c r="K50" t="n">
         <v>0.004702902244390622</v>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.08862487319394674</v>
+        <v>0.08862487319394675</v>
       </c>
       <c r="D51" t="n">
         <v>0.09543092552606913</v>
@@ -2294,22 +2294,22 @@
         <v>0.1232814351036308</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1464392529339593</v>
+        <v>0.1464392529339594</v>
       </c>
       <c r="G51" t="n">
         <v>0.1178723060828135</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1437480574961839</v>
+        <v>0.1437480574961838</v>
       </c>
       <c r="I51" t="n">
-        <v>0.153432054709483</v>
+        <v>0.1534320547094829</v>
       </c>
       <c r="J51" t="n">
         <v>0.172609808333714</v>
       </c>
       <c r="K51" t="n">
-        <v>0.165258800882279</v>
+        <v>0.1652588008822789</v>
       </c>
     </row>
     <row r="52">
@@ -2325,13 +2325,13 @@
         <v>0.003320255241938803</v>
       </c>
       <c r="D52" t="n">
-        <v>0.004110208674703264</v>
+        <v>0.004110208674703265</v>
       </c>
       <c r="E52" t="n">
         <v>0.004114405230317517</v>
       </c>
       <c r="F52" t="n">
-        <v>0.004815008964336458</v>
+        <v>0.004815008964336459</v>
       </c>
       <c r="G52" t="n">
         <v>0.003525898635423326</v>
@@ -2343,10 +2343,10 @@
         <v>0.004015576263568811</v>
       </c>
       <c r="J52" t="n">
-        <v>0.003941514147366282</v>
+        <v>0.003941514147366283</v>
       </c>
       <c r="K52" t="n">
-        <v>0.003098215572267926</v>
+        <v>0.003098215572267927</v>
       </c>
     </row>
     <row r="53">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.1293572896920879</v>
+        <v>0.129357289692088</v>
       </c>
       <c r="D54" t="n">
         <v>0.1325158134391979</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1177541805762791</v>
+        <v>0.1177541805762792</v>
       </c>
       <c r="F54" t="n">
         <v>0.1110281875953672</v>
@@ -2411,16 +2411,16 @@
         <v>0.0629253075505537</v>
       </c>
       <c r="H54" t="n">
-        <v>0.06607795532855953</v>
+        <v>0.06607795532855952</v>
       </c>
       <c r="I54" t="n">
-        <v>0.06906834059368386</v>
+        <v>0.06906834059368383</v>
       </c>
       <c r="J54" t="n">
-        <v>0.07499451485436789</v>
+        <v>0.07499451485436792</v>
       </c>
       <c r="K54" t="n">
-        <v>0.07269237711853423</v>
+        <v>0.07269237711853421</v>
       </c>
     </row>
     <row r="55">
@@ -2439,10 +2439,10 @@
         <v>0.04538750859701862</v>
       </c>
       <c r="E55" t="n">
-        <v>0.04409654593813859</v>
+        <v>0.04409654593813857</v>
       </c>
       <c r="F55" t="n">
-        <v>0.04430966747515475</v>
+        <v>0.04430966747515476</v>
       </c>
       <c r="G55" t="n">
         <v>0.030982833066642</v>
@@ -2451,7 +2451,7 @@
         <v>0.032971023076099</v>
       </c>
       <c r="I55" t="n">
-        <v>0.03460950172990835</v>
+        <v>0.03460950172990834</v>
       </c>
       <c r="J55" t="n">
         <v>0.03335091459233824</v>
@@ -2494,7 +2494,7 @@
         <v>0.04965374388186764</v>
       </c>
       <c r="K56" t="n">
-        <v>0.04085427355955476</v>
+        <v>0.04085427355955477</v>
       </c>
     </row>
     <row r="57">
@@ -2513,22 +2513,22 @@
         <v>0.005816999469441055</v>
       </c>
       <c r="E57" t="n">
-        <v>0.006720265248709325</v>
+        <v>0.006720265248709324</v>
       </c>
       <c r="F57" t="n">
         <v>0.007658827708579618</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0059198018050938</v>
+        <v>0.005919801805093801</v>
       </c>
       <c r="H57" t="n">
         <v>0.006444697641485714</v>
       </c>
       <c r="I57" t="n">
-        <v>0.006205398851210484</v>
+        <v>0.006205398851210483</v>
       </c>
       <c r="J57" t="n">
-        <v>0.005970130275676054</v>
+        <v>0.005970130275676053</v>
       </c>
       <c r="K57" t="n">
         <v>0.005148803505940616</v>
@@ -2547,10 +2547,10 @@
         <v>0.002003127785371184</v>
       </c>
       <c r="D58" t="n">
-        <v>0.002096395530434344</v>
+        <v>0.002096395530434345</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002248963516786319</v>
+        <v>0.002248963516786318</v>
       </c>
       <c r="F58" t="n">
         <v>0.002474620062536496</v>
@@ -2596,16 +2596,16 @@
         <v>0.004560995465968973</v>
       </c>
       <c r="H59" t="n">
-        <v>0.004460834226997032</v>
+        <v>0.004460834226997031</v>
       </c>
       <c r="I59" t="n">
         <v>0.005066884581949112</v>
       </c>
       <c r="J59" t="n">
-        <v>0.004887464632479526</v>
+        <v>0.004887464632479527</v>
       </c>
       <c r="K59" t="n">
-        <v>0.004199723737128104</v>
+        <v>0.004199723737128103</v>
       </c>
     </row>
     <row r="60">
@@ -2624,7 +2624,7 @@
         <v>0.02817777179408399</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03466469438127116</v>
+        <v>0.03466469438127118</v>
       </c>
       <c r="F60" t="n">
         <v>0.03684676778665802</v>
@@ -2633,7 +2633,7 @@
         <v>0.02465046090687941</v>
       </c>
       <c r="H60" t="n">
-        <v>0.02608926551890166</v>
+        <v>0.02608926551890165</v>
       </c>
       <c r="I60" t="n">
         <v>0.02830928869271764</v>
@@ -2642,7 +2642,7 @@
         <v>0.03403733877618028</v>
       </c>
       <c r="K60" t="n">
-        <v>0.03231732704830406</v>
+        <v>0.03231732704830405</v>
       </c>
     </row>
     <row r="61">
@@ -2667,7 +2667,7 @@
         <v>0.002377273823706544</v>
       </c>
       <c r="G61" t="n">
-        <v>0.001751224262576482</v>
+        <v>0.001751224262576483</v>
       </c>
       <c r="H61" t="n">
         <v>0.001917745921523563</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.05141757781294213</v>
+        <v>0.05141757781294214</v>
       </c>
       <c r="D63" t="n">
         <v>0.04578647403452128</v>
@@ -2744,13 +2744,13 @@
         <v>0.01952155743234689</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01896199492695701</v>
+        <v>0.018961994926957</v>
       </c>
       <c r="I63" t="n">
         <v>0.01868781952972002</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01914387885492053</v>
+        <v>0.01914387885492052</v>
       </c>
       <c r="K63" t="n">
         <v>0.01671946206811148</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.0006464760283687195</v>
+        <v>0.0006464760283687196</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0006929661012196427</v>
+        <v>0.0006929661012196426</v>
       </c>
       <c r="E64" t="n">
         <v>0.0008143506076510248</v>
@@ -2778,13 +2778,13 @@
         <v>0.0008943050073559698</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0007243777655798732</v>
+        <v>0.0007243777655798733</v>
       </c>
       <c r="H64" t="n">
         <v>0.0008064906517154805</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0008344007104429347</v>
+        <v>0.0008344007104429346</v>
       </c>
       <c r="J64" t="n">
         <v>0.0008490799223489287</v>
@@ -2818,13 +2818,13 @@
         <v>0.1976310377699713</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2308046188573601</v>
+        <v>0.23080461885736</v>
       </c>
       <c r="I65" t="n">
         <v>0.2076537646394028</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1777902662013681</v>
+        <v>0.1777902662013682</v>
       </c>
       <c r="K65" t="n">
         <v>0.1385932618558119</v>
@@ -2864,7 +2864,7 @@
         <v>0.004638895152155383</v>
       </c>
       <c r="K66" t="n">
-        <v>0.004223566926989411</v>
+        <v>0.004223566926989412</v>
       </c>
     </row>
     <row r="67">
@@ -2920,7 +2920,7 @@
         <v>0.002122673704408112</v>
       </c>
       <c r="E68" t="n">
-        <v>0.002003696490719206</v>
+        <v>0.002003696490719207</v>
       </c>
       <c r="F68" t="n">
         <v>0.00254173058626653</v>
@@ -2935,10 +2935,10 @@
         <v>0.001800773204911503</v>
       </c>
       <c r="J68" t="n">
-        <v>0.001785492594502766</v>
+        <v>0.001785492594502767</v>
       </c>
       <c r="K68" t="n">
-        <v>0.001907832746647338</v>
+        <v>0.001907832746647339</v>
       </c>
     </row>
     <row r="69">
@@ -2954,10 +2954,10 @@
         <v>0.002527572960762684</v>
       </c>
       <c r="D69" t="n">
-        <v>0.002498320188110934</v>
+        <v>0.002498320188110933</v>
       </c>
       <c r="E69" t="n">
-        <v>0.003559801060415183</v>
+        <v>0.003559801060415182</v>
       </c>
       <c r="F69" t="n">
         <v>0.004085579001517649</v>
@@ -3037,7 +3037,7 @@
         <v>0.05348877508857856</v>
       </c>
       <c r="G71" t="n">
-        <v>0.03312038058496635</v>
+        <v>0.03312038058496636</v>
       </c>
       <c r="H71" t="n">
         <v>0.03236154525095242</v>
@@ -3046,10 +3046,10 @@
         <v>0.03149287725507888</v>
       </c>
       <c r="J71" t="n">
-        <v>0.03543993296644582</v>
+        <v>0.03543993296644581</v>
       </c>
       <c r="K71" t="n">
-        <v>0.03171605868044941</v>
+        <v>0.0317160586804494</v>
       </c>
     </row>
     <row r="72">
@@ -3102,16 +3102,16 @@
         <v>0.03106582694992262</v>
       </c>
       <c r="D73" t="n">
-        <v>0.03195285511845901</v>
+        <v>0.031952855118459</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0314902064413734</v>
+        <v>0.03149020644137339</v>
       </c>
       <c r="F73" t="n">
-        <v>0.03176587109242849</v>
+        <v>0.0317658710924285</v>
       </c>
       <c r="G73" t="n">
-        <v>0.02288878203605947</v>
+        <v>0.02288878203605946</v>
       </c>
       <c r="H73" t="n">
         <v>0.02355703221144519</v>
@@ -3154,7 +3154,7 @@
         <v>0.01558050671397777</v>
       </c>
       <c r="I74" t="n">
-        <v>0.01562017092826867</v>
+        <v>0.01562017092826866</v>
       </c>
       <c r="J74" t="n">
         <v>0.01552475556652501</v>
@@ -3185,7 +3185,7 @@
         <v>0.0001989980776852568</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0002402299528239947</v>
+        <v>0.0002402299528239946</v>
       </c>
       <c r="H75" t="n">
         <v>0.0002624394955324227</v>
@@ -3194,7 +3194,7 @@
         <v>0.0002123325906290512</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0001831246411131478</v>
+        <v>0.0001831246411131477</v>
       </c>
       <c r="K75" t="n">
         <v>0.0001798548557858987</v>
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.005832176217312271</v>
+        <v>0.005832176217312269</v>
       </c>
       <c r="D76" t="n">
-        <v>0.005979781266118297</v>
+        <v>0.005979781266118296</v>
       </c>
       <c r="E76" t="n">
         <v>0.006050520688799263</v>
       </c>
       <c r="F76" t="n">
-        <v>0.006150279158141588</v>
+        <v>0.006150279158141587</v>
       </c>
       <c r="G76" t="n">
         <v>0.004238577510404527</v>
@@ -3228,13 +3228,13 @@
         <v>0.004529938406077664</v>
       </c>
       <c r="I76" t="n">
-        <v>0.00445071217898738</v>
+        <v>0.004450712178987379</v>
       </c>
       <c r="J76" t="n">
-        <v>0.004296995555855961</v>
+        <v>0.004296995555855962</v>
       </c>
       <c r="K76" t="n">
-        <v>0.003784476895892348</v>
+        <v>0.003784476895892347</v>
       </c>
     </row>
     <row r="77">
@@ -3265,7 +3265,7 @@
         <v>0.0004656877266761904</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0004576985796993836</v>
+        <v>0.0004576985796993837</v>
       </c>
       <c r="J77" t="n">
         <v>0.0004129886993790309</v>
@@ -3365,7 +3365,7 @@
         <v>0.001585932464450995</v>
       </c>
       <c r="F80" t="n">
-        <v>0.001734354885212928</v>
+        <v>0.001734354885212927</v>
       </c>
       <c r="G80" t="n">
         <v>0.00128839510207727</v>
@@ -3396,10 +3396,10 @@
         <v>0.0002916050805185422</v>
       </c>
       <c r="D81" t="n">
-        <v>0.000228102347904601</v>
+        <v>0.0002281023479046009</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0002337072289513307</v>
+        <v>0.0002337072289513306</v>
       </c>
       <c r="F81" t="n">
         <v>0.0002664341118563873</v>
@@ -3473,7 +3473,7 @@
         <v>0.01190402860628673</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01480979291233126</v>
+        <v>0.01480979291233127</v>
       </c>
       <c r="F83" t="n">
         <v>0.01698023950743058</v>
@@ -3485,7 +3485,7 @@
         <v>0.01517680994821645</v>
       </c>
       <c r="I83" t="n">
-        <v>0.01513343634495115</v>
+        <v>0.01513343634495114</v>
       </c>
       <c r="J83" t="n">
         <v>0.01763719949151174</v>
@@ -3519,7 +3519,7 @@
         <v>0.003999267224337631</v>
       </c>
       <c r="H84" t="n">
-        <v>0.004746767959585513</v>
+        <v>0.004746767959585514</v>
       </c>
       <c r="I84" t="n">
         <v>0.004794670429389416</v>
@@ -3658,10 +3658,10 @@
         <v>0.009226706034643732</v>
       </c>
       <c r="G88" t="n">
-        <v>0.004966564819157158</v>
+        <v>0.004966564819157159</v>
       </c>
       <c r="H88" t="n">
-        <v>0.004022427706455933</v>
+        <v>0.004022427706455932</v>
       </c>
       <c r="I88" t="n">
         <v>0.003239280853386292</v>
@@ -3711,13 +3711,13 @@
         <v>0.006455831259552874</v>
       </c>
       <c r="F90" t="n">
-        <v>0.007354630455405434</v>
+        <v>0.007354630455405433</v>
       </c>
       <c r="G90" t="n">
-        <v>0.005694709803659429</v>
+        <v>0.00569470980365943</v>
       </c>
       <c r="H90" t="n">
-        <v>0.006183340868930652</v>
+        <v>0.006183340868930653</v>
       </c>
       <c r="I90" t="n">
         <v>0.005942918499485889</v>
@@ -3779,13 +3779,13 @@
         <v>0.0006063470036233152</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0006288400893236631</v>
+        <v>0.000628840089323663</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0007540811756235989</v>
+        <v>0.0007540811756235988</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0009105012887387924</v>
+        <v>0.0009105012887387925</v>
       </c>
       <c r="G92" t="n">
         <v>0.000619772644811769</v>
@@ -3797,7 +3797,7 @@
         <v>0.000760820769536521</v>
       </c>
       <c r="J92" t="n">
-        <v>0.0007478689774331702</v>
+        <v>0.00074786897743317</v>
       </c>
       <c r="K92" t="n">
         <v>0.0005260838377134806</v>
@@ -3896,7 +3896,7 @@
         <v>0.01362820297217727</v>
       </c>
       <c r="F95" t="n">
-        <v>0.01347140919449485</v>
+        <v>0.01347140919449486</v>
       </c>
       <c r="G95" t="n">
         <v>0.01023292119299727</v>
@@ -3905,10 +3905,10 @@
         <v>0.01091487895704812</v>
       </c>
       <c r="I95" t="n">
-        <v>0.01007454514383092</v>
+        <v>0.01007454514383093</v>
       </c>
       <c r="J95" t="n">
-        <v>0.005619761396485067</v>
+        <v>0.005619761396485066</v>
       </c>
       <c r="K95" t="n">
         <v>0.003362647696177781</v>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.0005902692361788423</v>
+        <v>0.0005902692361788424</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0005763992389834753</v>
+        <v>0.0005763992389834754</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0007835235514515853</v>
+        <v>0.0007835235514515854</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0009154253324582467</v>
+        <v>0.0009154253324582469</v>
       </c>
       <c r="G97" t="n">
         <v>0.0007159131477770084</v>
@@ -4019,7 +4019,7 @@
         <v>0.002801225225552152</v>
       </c>
       <c r="J98" t="n">
-        <v>0.002778027994755366</v>
+        <v>0.002778027994755365</v>
       </c>
       <c r="K98" t="n">
         <v>0.00243798359102109</v>
@@ -4044,7 +4044,7 @@
         <v>0.001937497600621981</v>
       </c>
       <c r="F99" t="n">
-        <v>0.002335155844745968</v>
+        <v>0.002335155844745969</v>
       </c>
       <c r="G99" t="n">
         <v>0.001936824317460581</v>
@@ -4053,7 +4053,7 @@
         <v>0.002397240809520054</v>
       </c>
       <c r="I99" t="n">
-        <v>0.002760483011136189</v>
+        <v>0.00276048301113619</v>
       </c>
       <c r="J99" t="n">
         <v>0.00246287752843205</v>
@@ -4075,7 +4075,7 @@
         <v>0.001450273856057479</v>
       </c>
       <c r="D100" t="n">
-        <v>0.001546095477902458</v>
+        <v>0.001546095477902457</v>
       </c>
       <c r="E100" t="n">
         <v>0.001903552969237831</v>
@@ -4096,7 +4096,7 @@
         <v>0.0016635304771847</v>
       </c>
       <c r="K100" t="n">
-        <v>0.001437290708212476</v>
+        <v>0.001437290708212475</v>
       </c>
     </row>
     <row r="101">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.000926662438830794</v>
+        <v>0.0009266624388307942</v>
       </c>
       <c r="D101" t="n">
         <v>0.0009019974555726224</v>
@@ -4133,7 +4133,7 @@
         <v>0.001025877105140709</v>
       </c>
       <c r="K101" t="n">
-        <v>0.0009749146761976045</v>
+        <v>0.0009749146761976048</v>
       </c>
     </row>
     <row r="102">
@@ -4164,7 +4164,7 @@
         <v>0.0179004635780695</v>
       </c>
       <c r="I102" t="n">
-        <v>0.01832832432940201</v>
+        <v>0.01832832432940202</v>
       </c>
       <c r="J102" t="n">
         <v>0.01701003026854208</v>
@@ -4189,7 +4189,7 @@
         <v>0.0002943969356991125</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0004046109446869879</v>
+        <v>0.000404610944686988</v>
       </c>
       <c r="F103" t="n">
         <v>0.0003703962212134172</v>
@@ -4198,7 +4198,7 @@
         <v>0.0002948271160707808</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0003934351560906973</v>
+        <v>0.0003934351560906974</v>
       </c>
       <c r="I103" t="n">
         <v>0.0003724358235328003</v>
@@ -4232,19 +4232,19 @@
         <v>0.001198706306301318</v>
       </c>
       <c r="G104" t="n">
-        <v>0.000988169405270662</v>
+        <v>0.0009881694052706618</v>
       </c>
       <c r="H104" t="n">
         <v>0.001051727260458074</v>
       </c>
       <c r="I104" t="n">
-        <v>0.001171952875883823</v>
+        <v>0.001171952875883822</v>
       </c>
       <c r="J104" t="n">
         <v>0.001206764422356142</v>
       </c>
       <c r="K104" t="n">
-        <v>0.0009583892745168355</v>
+        <v>0.0009583892745168353</v>
       </c>
     </row>
     <row r="105">
@@ -4263,7 +4263,7 @@
         <v>0.002757248125215705</v>
       </c>
       <c r="E105" t="n">
-        <v>0.003421940671249286</v>
+        <v>0.003421940671249285</v>
       </c>
       <c r="F105" t="n">
         <v>0.003660446878551815</v>
@@ -4281,7 +4281,7 @@
         <v>0.002883040613036465</v>
       </c>
       <c r="K105" t="n">
-        <v>0.002572200645614519</v>
+        <v>0.00257220064561452</v>
       </c>
     </row>
     <row r="106">
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.008215476261486443</v>
+        <v>0.008215476261486445</v>
       </c>
       <c r="D108" t="n">
-        <v>0.007666625751012304</v>
+        <v>0.007666625751012305</v>
       </c>
       <c r="E108" t="n">
-        <v>0.008634178001036318</v>
+        <v>0.008634178001036316</v>
       </c>
       <c r="F108" t="n">
         <v>0.009242657580346966</v>
@@ -4386,7 +4386,7 @@
         <v>0.007864022269710174</v>
       </c>
       <c r="I108" t="n">
-        <v>0.00754032248081667</v>
+        <v>0.007540322480816671</v>
       </c>
       <c r="J108" t="n">
         <v>0.007412815937327969</v>
@@ -4482,28 +4482,28 @@
         <v>0.02834701846647128</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0277735275783245</v>
+        <v>0.02777352757832451</v>
       </c>
       <c r="E111" t="n">
         <v>0.02973889874818716</v>
       </c>
       <c r="F111" t="n">
-        <v>0.03168891815276603</v>
+        <v>0.03168891815276602</v>
       </c>
       <c r="G111" t="n">
         <v>0.02253679374114307</v>
       </c>
       <c r="H111" t="n">
-        <v>0.02364800131711196</v>
+        <v>0.02364800131711197</v>
       </c>
       <c r="I111" t="n">
         <v>0.02280011303787581</v>
       </c>
       <c r="J111" t="n">
-        <v>0.0216682399673169</v>
+        <v>0.02166823996731691</v>
       </c>
       <c r="K111" t="n">
-        <v>0.01986144014040185</v>
+        <v>0.01986144014040184</v>
       </c>
     </row>
     <row r="112">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.006258061839065454</v>
+        <v>0.006258061839065453</v>
       </c>
       <c r="D112" t="n">
         <v>0.006184879714943886</v>
@@ -4540,7 +4540,7 @@
         <v>0.006445812187888319</v>
       </c>
       <c r="K112" t="n">
-        <v>0.005563853686088567</v>
+        <v>0.005563853686088566</v>
       </c>
     </row>
     <row r="113">
@@ -4590,13 +4590,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.0006595170715311797</v>
+        <v>0.0006595170715311796</v>
       </c>
       <c r="D114" t="n">
         <v>0.0006737288016188098</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0009005933663121521</v>
+        <v>0.000900593366312152</v>
       </c>
       <c r="F114" t="n">
         <v>0.0009655650236984076</v>
@@ -4605,16 +4605,16 @@
         <v>0.0007899091120744023</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0008539262289318009</v>
+        <v>0.000853926228931801</v>
       </c>
       <c r="I114" t="n">
         <v>0.0007938774992698838</v>
       </c>
       <c r="J114" t="n">
-        <v>0.0008860946897069331</v>
+        <v>0.0008860946897069332</v>
       </c>
       <c r="K114" t="n">
-        <v>0.0007601697973936518</v>
+        <v>0.0007601697973936516</v>
       </c>
     </row>
     <row r="115">
@@ -4633,10 +4633,10 @@
         <v>0.006901243062638507</v>
       </c>
       <c r="E115" t="n">
-        <v>0.008202522239654099</v>
+        <v>0.008202522239654101</v>
       </c>
       <c r="F115" t="n">
-        <v>0.009220325865391314</v>
+        <v>0.009220325865391312</v>
       </c>
       <c r="G115" t="n">
         <v>0.006801781128885183</v>
@@ -4645,10 +4645,10 @@
         <v>0.007476194060053779</v>
       </c>
       <c r="I115" t="n">
-        <v>0.007450757558230522</v>
+        <v>0.007450757558230523</v>
       </c>
       <c r="J115" t="n">
-        <v>0.007771385689772542</v>
+        <v>0.007771385689772543</v>
       </c>
       <c r="K115" t="n">
         <v>0.007002867702895481</v>
@@ -4775,28 +4775,28 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.004535783091963973</v>
+        <v>0.004535783091963974</v>
       </c>
       <c r="D119" t="n">
-        <v>0.005351840800355665</v>
+        <v>0.005351840800355667</v>
       </c>
       <c r="E119" t="n">
         <v>0.007494312660224909</v>
       </c>
       <c r="F119" t="n">
-        <v>0.008314491969159838</v>
+        <v>0.008314491969159836</v>
       </c>
       <c r="G119" t="n">
-        <v>0.006166717970470551</v>
+        <v>0.00616671797047055</v>
       </c>
       <c r="H119" t="n">
         <v>0.006395686472207411</v>
       </c>
       <c r="I119" t="n">
-        <v>0.007295041058042475</v>
+        <v>0.007295041058042476</v>
       </c>
       <c r="J119" t="n">
-        <v>0.005957577401484551</v>
+        <v>0.00595757740148455</v>
       </c>
       <c r="K119" t="n">
         <v>0.005439615983385745</v>
@@ -4815,28 +4815,28 @@
         <v>0.2072315998985687</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2265413696157169</v>
+        <v>0.2265413696157171</v>
       </c>
       <c r="E120" t="n">
-        <v>0.30130593377159</v>
+        <v>0.3013059337715899</v>
       </c>
       <c r="F120" t="n">
-        <v>0.3643677917357575</v>
+        <v>0.3643677917357577</v>
       </c>
       <c r="G120" t="n">
-        <v>0.2960894294742227</v>
+        <v>0.2960894294742228</v>
       </c>
       <c r="H120" t="n">
         <v>0.3669573136851952</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3890209431623528</v>
+        <v>0.3890209431623527</v>
       </c>
       <c r="J120" t="n">
-        <v>0.4438728227601075</v>
+        <v>0.4438728227601074</v>
       </c>
       <c r="K120" t="n">
-        <v>0.4179484604164822</v>
+        <v>0.4179484604164821</v>
       </c>
     </row>
     <row r="121">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.009298083343975611</v>
+        <v>0.009298083343975609</v>
       </c>
       <c r="D123" t="n">
         <v>0.008512861433854211</v>
@@ -4935,19 +4935,19 @@
         <v>0.01027483536059101</v>
       </c>
       <c r="G123" t="n">
-        <v>0.007837442443484929</v>
+        <v>0.007837442443484928</v>
       </c>
       <c r="H123" t="n">
         <v>0.008632041377239899</v>
       </c>
       <c r="I123" t="n">
-        <v>0.008615842867764319</v>
+        <v>0.008615842867764321</v>
       </c>
       <c r="J123" t="n">
         <v>0.009185361710059636</v>
       </c>
       <c r="K123" t="n">
-        <v>0.008393337534483611</v>
+        <v>0.008393337534483613</v>
       </c>
     </row>
     <row r="124">
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.002456823482008936</v>
+        <v>0.002456823482008937</v>
       </c>
       <c r="D125" t="n">
         <v>0.002560891341550809</v>
@@ -5021,7 +5021,7 @@
         <v>0.001121116725691162</v>
       </c>
       <c r="K125" t="n">
-        <v>0.0009596996184378776</v>
+        <v>0.0009596996184378775</v>
       </c>
     </row>
     <row r="126">
@@ -5074,10 +5074,10 @@
         <v>0.0006452788618865257</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0005960210291018335</v>
+        <v>0.0005960210291018338</v>
       </c>
       <c r="E127" t="n">
-        <v>0.0007367673584396598</v>
+        <v>0.0007367673584396597</v>
       </c>
       <c r="F127" t="n">
         <v>0.0008481641581135404</v>
@@ -5089,7 +5089,7 @@
         <v>0.0007937054893220945</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0007738908419271542</v>
+        <v>0.0007738908419271544</v>
       </c>
       <c r="J127" t="n">
         <v>0.0007468015087878287</v>
@@ -5166,7 +5166,7 @@
         <v>0.001481452565965569</v>
       </c>
       <c r="J129" t="n">
-        <v>0.001556560337333499</v>
+        <v>0.0015565603373335</v>
       </c>
       <c r="K129" t="n">
         <v>0.00145401784195625</v>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.000968777565441583</v>
+        <v>0.0009687775654415829</v>
       </c>
       <c r="D131" t="n">
-        <v>0.0009766199081426327</v>
+        <v>0.0009766199081426329</v>
       </c>
       <c r="E131" t="n">
-        <v>0.001255795640485143</v>
+        <v>0.001255795640485144</v>
       </c>
       <c r="F131" t="n">
         <v>0.001442051854239236</v>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.0007121753321042924</v>
+        <v>0.0007121753321042925</v>
       </c>
       <c r="D135" t="n">
         <v>0.0007264682649995678</v>
@@ -5502,7 +5502,7 @@
         <v>0.0001596155646565328</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0001871757424570962</v>
+        <v>0.0001871757424570961</v>
       </c>
       <c r="E139" t="n">
         <v>0.0001781356121911384</v>
@@ -5511,7 +5511,7 @@
         <v>0.0002169567892669661</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0001654877152033462</v>
+        <v>0.0001654877152033463</v>
       </c>
       <c r="H139" t="n">
         <v>0.0001963169642382556</v>
